--- a/tests/regression_artifacts/downloads/email_TSCW18489131_budget_marine_grenada/current/90062.xlsx
+++ b/tests/regression_artifacts/downloads/email_TSCW18489131_budget_marine_grenada/current/90062.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invoice Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Invoice Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM41"/>
+  <dimension ref="A1:AM39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1425,12 +1425,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Rubber and articles thereof</t>
+          <t>GASKETS &amp; SEALS</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40169990</t>
+          <t>40169300</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -1489,7 +1489,7 @@
       <c r="AJ10" s="2" t="n"/>
       <c r="AK10" s="2" t="inlineStr">
         <is>
-          <t>40169990</t>
+          <t>40169300</t>
         </is>
       </c>
     </row>
@@ -1508,7 +1508,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Plastics and articles thereof</t>
+          <t>Articles of iron or steel</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Marine propulsion parts</t>
+          <t>Ships' or boats' propellers and blades therefor</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Moulding boxes for metal foundry</t>
+          <t>Articles of iron or steel</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2320,7 +2320,7 @@
       <c r="I25" s="7" t="n"/>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>CET (weighted avg 12.4%)</t>
+          <t>CET (weighted avg 10.0%)</t>
         </is>
       </c>
       <c r="K25" s="7" t="n"/>
@@ -2329,7 +2329,7 @@
       <c r="N25" s="7" t="n"/>
       <c r="O25" s="7" t="n"/>
       <c r="P25" s="9" t="n">
-        <v>237.52</v>
+        <v>192.82</v>
       </c>
       <c r="Q25" s="7" t="n"/>
       <c r="R25" s="7" t="n"/>
@@ -2365,7 +2365,7 @@
       <c r="I26" s="7" t="n"/>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └ 40169300: 20% CET (7% of value)</t>
+          <t xml:space="preserve">  └ 40169300: 20% CET (9% of value)</t>
         </is>
       </c>
       <c r="K26" s="7" t="n"/>
@@ -2374,7 +2374,7 @@
       <c r="N26" s="7" t="n"/>
       <c r="O26" s="7" t="n"/>
       <c r="P26" s="9" t="n">
-        <v>27.98</v>
+        <v>34.3</v>
       </c>
       <c r="Q26" s="7" t="n"/>
       <c r="R26" s="7" t="n"/>
@@ -2410,7 +2410,7 @@
       <c r="I27" s="7" t="n"/>
       <c r="J27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └ 40169990: 20% CET (2% of value)</t>
+          <t xml:space="preserve">  └ 73079900: 20% CET (3% of value)</t>
         </is>
       </c>
       <c r="K27" s="7" t="n"/>
@@ -2419,7 +2419,7 @@
       <c r="N27" s="7" t="n"/>
       <c r="O27" s="7" t="n"/>
       <c r="P27" s="9" t="n">
-        <v>6.32</v>
+        <v>12.19</v>
       </c>
       <c r="Q27" s="7" t="n"/>
       <c r="R27" s="7" t="n"/>
@@ -2455,7 +2455,7 @@
       <c r="I28" s="7" t="n"/>
       <c r="J28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └ 73079900: 20% CET (3% of value)</t>
+          <t xml:space="preserve">  └ 73182900: 20% CET (1% of value)</t>
         </is>
       </c>
       <c r="K28" s="7" t="n"/>
@@ -2464,7 +2464,7 @@
       <c r="N28" s="7" t="n"/>
       <c r="O28" s="7" t="n"/>
       <c r="P28" s="9" t="n">
-        <v>12.19</v>
+        <v>5.45</v>
       </c>
       <c r="Q28" s="7" t="n"/>
       <c r="R28" s="7" t="n"/>
@@ -2500,7 +2500,7 @@
       <c r="I29" s="7" t="n"/>
       <c r="J29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └ 73182900: 20% CET (1% of value)</t>
+          <t xml:space="preserve">  └ 84099120: 5% CET (11% of value)</t>
         </is>
       </c>
       <c r="K29" s="7" t="n"/>
@@ -2509,7 +2509,7 @@
       <c r="N29" s="7" t="n"/>
       <c r="O29" s="7" t="n"/>
       <c r="P29" s="9" t="n">
-        <v>5.45</v>
+        <v>10.26</v>
       </c>
       <c r="Q29" s="7" t="n"/>
       <c r="R29" s="7" t="n"/>
@@ -2545,7 +2545,7 @@
       <c r="I30" s="7" t="n"/>
       <c r="J30" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └ 84099120: 5% CET (11% of value)</t>
+          <t xml:space="preserve">  └ 84139190: 5% CET (4% of value)</t>
         </is>
       </c>
       <c r="K30" s="7" t="n"/>
@@ -2554,7 +2554,7 @@
       <c r="N30" s="7" t="n"/>
       <c r="O30" s="7" t="n"/>
       <c r="P30" s="9" t="n">
-        <v>10.26</v>
+        <v>3.49</v>
       </c>
       <c r="Q30" s="7" t="n"/>
       <c r="R30" s="7" t="n"/>
@@ -2590,7 +2590,7 @@
       <c r="I31" s="7" t="n"/>
       <c r="J31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └ 84139190: 5% CET (4% of value)</t>
+          <t xml:space="preserve">  └ 84871000: 5% CET (31% of value)</t>
         </is>
       </c>
       <c r="K31" s="7" t="n"/>
@@ -2599,7 +2599,7 @@
       <c r="N31" s="7" t="n"/>
       <c r="O31" s="7" t="n"/>
       <c r="P31" s="9" t="n">
-        <v>3.49</v>
+        <v>29.8</v>
       </c>
       <c r="Q31" s="7" t="n"/>
       <c r="R31" s="7" t="n"/>
@@ -2635,7 +2635,7 @@
       <c r="I32" s="7" t="n"/>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └ 84801000: 5% CET (4% of value)</t>
+          <t xml:space="preserve">  └ 84879000: 5% CET (17% of value)</t>
         </is>
       </c>
       <c r="K32" s="7" t="n"/>
@@ -2644,7 +2644,7 @@
       <c r="N32" s="7" t="n"/>
       <c r="O32" s="7" t="n"/>
       <c r="P32" s="9" t="n">
-        <v>4.1</v>
+        <v>16.21</v>
       </c>
       <c r="Q32" s="7" t="n"/>
       <c r="R32" s="7" t="n"/>
@@ -2680,7 +2680,7 @@
       <c r="I33" s="7" t="n"/>
       <c r="J33" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └ 84871000: 5% CET (16% of value)</t>
+          <t xml:space="preserve">  └ 85113000: 20% CET (11% of value)</t>
         </is>
       </c>
       <c r="K33" s="7" t="n"/>
@@ -2689,7 +2689,7 @@
       <c r="N33" s="7" t="n"/>
       <c r="O33" s="7" t="n"/>
       <c r="P33" s="9" t="n">
-        <v>14.9</v>
+        <v>42.22</v>
       </c>
       <c r="Q33" s="7" t="n"/>
       <c r="R33" s="7" t="n"/>
@@ -2725,7 +2725,7 @@
       <c r="I34" s="7" t="n"/>
       <c r="J34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └ 84879000: 5% CET (17% of value)</t>
+          <t xml:space="preserve">  └ 85365000: 20% CET (9% of value)</t>
         </is>
       </c>
       <c r="K34" s="7" t="n"/>
@@ -2734,7 +2734,7 @@
       <c r="N34" s="7" t="n"/>
       <c r="O34" s="7" t="n"/>
       <c r="P34" s="9" t="n">
-        <v>16.21</v>
+        <v>34.8</v>
       </c>
       <c r="Q34" s="7" t="n"/>
       <c r="R34" s="7" t="n"/>
@@ -2770,7 +2770,7 @@
       <c r="I35" s="7" t="n"/>
       <c r="J35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └ 85113000: 20% CET (11% of value)</t>
+          <t xml:space="preserve">  └ 86080000: 5% CET (4% of value)</t>
         </is>
       </c>
       <c r="K35" s="7" t="n"/>
@@ -2779,7 +2779,7 @@
       <c r="N35" s="7" t="n"/>
       <c r="O35" s="7" t="n"/>
       <c r="P35" s="9" t="n">
-        <v>42.22</v>
+        <v>4.1</v>
       </c>
       <c r="Q35" s="7" t="n"/>
       <c r="R35" s="7" t="n"/>
@@ -2815,7 +2815,7 @@
       <c r="I36" s="7" t="n"/>
       <c r="J36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └ 85365000: 20% CET (9% of value)</t>
+          <t>CSC (6%)</t>
         </is>
       </c>
       <c r="K36" s="7" t="n"/>
@@ -2824,7 +2824,7 @@
       <c r="N36" s="7" t="n"/>
       <c r="O36" s="7" t="n"/>
       <c r="P36" s="9" t="n">
-        <v>34.8</v>
+        <v>115.32</v>
       </c>
       <c r="Q36" s="7" t="n"/>
       <c r="R36" s="7" t="n"/>
@@ -2860,7 +2860,7 @@
       <c r="I37" s="7" t="n"/>
       <c r="J37" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └ 88073000: 20% CET (16% of value)</t>
+          <t>VAT (15%) on CIF+CET+CSC</t>
         </is>
       </c>
       <c r="K37" s="7" t="n"/>
@@ -2869,7 +2869,7 @@
       <c r="N37" s="7" t="n"/>
       <c r="O37" s="7" t="n"/>
       <c r="P37" s="9" t="n">
-        <v>59.59</v>
+        <v>334.53</v>
       </c>
       <c r="Q37" s="7" t="n"/>
       <c r="R37" s="7" t="n"/>
@@ -2894,49 +2894,49 @@
       <c r="AK37" s="7" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="n"/>
-      <c r="B38" s="7" t="n"/>
-      <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7" t="n"/>
-      <c r="E38" s="7" t="n"/>
-      <c r="F38" s="7" t="n"/>
-      <c r="G38" s="7" t="n"/>
-      <c r="H38" s="7" t="n"/>
-      <c r="I38" s="7" t="n"/>
-      <c r="J38" s="8" t="inlineStr">
-        <is>
-          <t>CSC (6%)</t>
-        </is>
-      </c>
-      <c r="K38" s="7" t="n"/>
-      <c r="L38" s="7" t="n"/>
-      <c r="M38" s="7" t="n"/>
-      <c r="N38" s="7" t="n"/>
-      <c r="O38" s="7" t="n"/>
-      <c r="P38" s="9" t="n">
-        <v>115.32</v>
-      </c>
-      <c r="Q38" s="7" t="n"/>
-      <c r="R38" s="7" t="n"/>
-      <c r="S38" s="7" t="n"/>
-      <c r="T38" s="7" t="n"/>
-      <c r="U38" s="7" t="n"/>
-      <c r="V38" s="7" t="n"/>
-      <c r="W38" s="7" t="n"/>
-      <c r="X38" s="7" t="n"/>
-      <c r="Y38" s="7" t="n"/>
-      <c r="Z38" s="7" t="n"/>
-      <c r="AA38" s="7" t="n"/>
-      <c r="AB38" s="7" t="n"/>
-      <c r="AC38" s="7" t="n"/>
-      <c r="AD38" s="7" t="n"/>
-      <c r="AE38" s="7" t="n"/>
-      <c r="AF38" s="7" t="n"/>
-      <c r="AG38" s="7" t="n"/>
-      <c r="AH38" s="7" t="n"/>
-      <c r="AI38" s="7" t="n"/>
-      <c r="AJ38" s="7" t="n"/>
-      <c r="AK38" s="7" t="n"/>
+      <c r="A38" s="10" t="n"/>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
+      <c r="G38" s="10" t="n"/>
+      <c r="H38" s="10" t="n"/>
+      <c r="I38" s="10" t="n"/>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>ESTIMATED TOTAL DUTIES</t>
+        </is>
+      </c>
+      <c r="K38" s="10" t="n"/>
+      <c r="L38" s="10" t="n"/>
+      <c r="M38" s="10" t="n"/>
+      <c r="N38" s="10" t="n"/>
+      <c r="O38" s="10" t="n"/>
+      <c r="P38" s="11" t="n">
+        <v>642.67</v>
+      </c>
+      <c r="Q38" s="10" t="n"/>
+      <c r="R38" s="10" t="n"/>
+      <c r="S38" s="10" t="n"/>
+      <c r="T38" s="10" t="n"/>
+      <c r="U38" s="10" t="n"/>
+      <c r="V38" s="10" t="n"/>
+      <c r="W38" s="10" t="n"/>
+      <c r="X38" s="10" t="n"/>
+      <c r="Y38" s="10" t="n"/>
+      <c r="Z38" s="10" t="n"/>
+      <c r="AA38" s="10" t="n"/>
+      <c r="AB38" s="10" t="n"/>
+      <c r="AC38" s="10" t="n"/>
+      <c r="AD38" s="10" t="n"/>
+      <c r="AE38" s="10" t="n"/>
+      <c r="AF38" s="10" t="n"/>
+      <c r="AG38" s="10" t="n"/>
+      <c r="AH38" s="10" t="n"/>
+      <c r="AI38" s="10" t="n"/>
+      <c r="AJ38" s="10" t="n"/>
+      <c r="AK38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n"/>
@@ -2950,7 +2950,7 @@
       <c r="I39" s="7" t="n"/>
       <c r="J39" s="8" t="inlineStr">
         <is>
-          <t>VAT (15%) on CIF+CET+CSC</t>
+          <t>Effective Duty Rate</t>
         </is>
       </c>
       <c r="K39" s="7" t="n"/>
@@ -2958,8 +2958,8 @@
       <c r="M39" s="7" t="n"/>
       <c r="N39" s="7" t="n"/>
       <c r="O39" s="7" t="n"/>
-      <c r="P39" s="9" t="n">
-        <v>341.23</v>
+      <c r="P39" s="12" t="n">
+        <v>0.3343686915985099</v>
       </c>
       <c r="Q39" s="7" t="n"/>
       <c r="R39" s="7" t="n"/>
@@ -2983,96 +2983,6 @@
       <c r="AJ39" s="7" t="n"/>
       <c r="AK39" s="7" t="n"/>
     </row>
-    <row r="40">
-      <c r="A40" s="10" t="n"/>
-      <c r="B40" s="10" t="n"/>
-      <c r="C40" s="10" t="n"/>
-      <c r="D40" s="10" t="n"/>
-      <c r="E40" s="10" t="n"/>
-      <c r="F40" s="10" t="n"/>
-      <c r="G40" s="10" t="n"/>
-      <c r="H40" s="10" t="n"/>
-      <c r="I40" s="10" t="n"/>
-      <c r="J40" s="6" t="inlineStr">
-        <is>
-          <t>ESTIMATED TOTAL DUTIES</t>
-        </is>
-      </c>
-      <c r="K40" s="10" t="n"/>
-      <c r="L40" s="10" t="n"/>
-      <c r="M40" s="10" t="n"/>
-      <c r="N40" s="10" t="n"/>
-      <c r="O40" s="10" t="n"/>
-      <c r="P40" s="11" t="n">
-        <v>694.0700000000001</v>
-      </c>
-      <c r="Q40" s="10" t="n"/>
-      <c r="R40" s="10" t="n"/>
-      <c r="S40" s="10" t="n"/>
-      <c r="T40" s="10" t="n"/>
-      <c r="U40" s="10" t="n"/>
-      <c r="V40" s="10" t="n"/>
-      <c r="W40" s="10" t="n"/>
-      <c r="X40" s="10" t="n"/>
-      <c r="Y40" s="10" t="n"/>
-      <c r="Z40" s="10" t="n"/>
-      <c r="AA40" s="10" t="n"/>
-      <c r="AB40" s="10" t="n"/>
-      <c r="AC40" s="10" t="n"/>
-      <c r="AD40" s="10" t="n"/>
-      <c r="AE40" s="10" t="n"/>
-      <c r="AF40" s="10" t="n"/>
-      <c r="AG40" s="10" t="n"/>
-      <c r="AH40" s="10" t="n"/>
-      <c r="AI40" s="10" t="n"/>
-      <c r="AJ40" s="10" t="n"/>
-      <c r="AK40" s="10" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="n"/>
-      <c r="B41" s="7" t="n"/>
-      <c r="C41" s="7" t="n"/>
-      <c r="D41" s="7" t="n"/>
-      <c r="E41" s="7" t="n"/>
-      <c r="F41" s="7" t="n"/>
-      <c r="G41" s="7" t="n"/>
-      <c r="H41" s="7" t="n"/>
-      <c r="I41" s="7" t="n"/>
-      <c r="J41" s="8" t="inlineStr">
-        <is>
-          <t>Effective Duty Rate</t>
-        </is>
-      </c>
-      <c r="K41" s="7" t="n"/>
-      <c r="L41" s="7" t="n"/>
-      <c r="M41" s="7" t="n"/>
-      <c r="N41" s="7" t="n"/>
-      <c r="O41" s="7" t="n"/>
-      <c r="P41" s="12" t="n">
-        <v>0.3611111111111112</v>
-      </c>
-      <c r="Q41" s="7" t="n"/>
-      <c r="R41" s="7" t="n"/>
-      <c r="S41" s="7" t="n"/>
-      <c r="T41" s="7" t="n"/>
-      <c r="U41" s="7" t="n"/>
-      <c r="V41" s="7" t="n"/>
-      <c r="W41" s="7" t="n"/>
-      <c r="X41" s="7" t="n"/>
-      <c r="Y41" s="7" t="n"/>
-      <c r="Z41" s="7" t="n"/>
-      <c r="AA41" s="7" t="n"/>
-      <c r="AB41" s="7" t="n"/>
-      <c r="AC41" s="7" t="n"/>
-      <c r="AD41" s="7" t="n"/>
-      <c r="AE41" s="7" t="n"/>
-      <c r="AF41" s="7" t="n"/>
-      <c r="AG41" s="7" t="n"/>
-      <c r="AH41" s="7" t="n"/>
-      <c r="AI41" s="7" t="n"/>
-      <c r="AJ41" s="7" t="n"/>
-      <c r="AK41" s="7" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
